--- a/Kensington_Ratings.xlsx
+++ b/Kensington_Ratings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kensington" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Kensington" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="35" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,6 +527,11 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Google Maps Name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Excluded Sources</t>
         </is>
       </c>
     </row>
@@ -557,6 +563,7 @@
           <t>Emilia</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,6 +593,7 @@
           <t>Fiore</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,6 +623,7 @@
           <t>Picnic</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,6 +653,7 @@
           <t>DreamWorld Bakes</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -673,6 +683,7 @@
           <t>Zig Zag BBQ</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +713,7 @@
           <t>Yuhiro Omakase Sushi</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -731,6 +743,7 @@
           <t>Little Walter’s</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -760,6 +773,7 @@
           <t>FORÎN</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -789,6 +803,7 @@
           <t>Emmett</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -818,6 +833,7 @@
           <t>Kalaya</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,6 +863,7 @@
           <t>Tulip Pasta &amp; Wine Bar</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -876,6 +893,7 @@
           <t>Suraya Restaurant</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -905,6 +923,7 @@
           <t>El Chingon Fishtown</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,6 +953,7 @@
           <t>PIZZA Shackamaxon</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -963,6 +983,7 @@
           <t>Marina’s Pizza</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -992,6 +1013,7 @@
           <t>Loco Pez</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1021,6 +1043,7 @@
           <t>Gilda</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1050,6 +1073,7 @@
           <t>Amá</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1079,6 +1103,7 @@
           <t>Wm. Mulherin’s Sons</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1108,6 +1133,7 @@
           <t>Two Robbers Fishtown</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1137,6 +1163,7 @@
           <t>HIROKI</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1166,6 +1193,7 @@
           <t>Amy's Pastelillos</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1195,6 +1223,7 @@
           <t>Laser Wolf</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1224,6 +1253,7 @@
           <t>Middle Child Clubhouse</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1253,6 +1283,7 @@
           <t>Pizzeria Beddia</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1282,6 +1313,7 @@
           <t>Jaffa Bar</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1311,6 +1343,7 @@
           <t>Liberty Kitchen PHL</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1340,6 +1373,7 @@
           <t>Sor Ynez</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1369,6 +1403,7 @@
           <t>LMNO</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1398,6 +1433,7 @@
           <t>Helm</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1427,6 +1463,7 @@
           <t>CHAR</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
